--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9405,7 +9405,7 @@
         <v>109511138</v>
       </c>
       <c r="B75" t="n">
-        <v>56683</v>
+        <v>56688</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9420,11 +9420,6 @@
       <c r="E75" t="n">
         <v>100038</v>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Skogsduva</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>Columba oenas</t>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9405,7 +9405,7 @@
         <v>109511138</v>
       </c>
       <c r="B75" t="n">
-        <v>56688</v>
+        <v>56692</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9419,6 +9419,11 @@
       </c>
       <c r="E75" t="n">
         <v>100038</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9405,7 +9405,7 @@
         <v>109511138</v>
       </c>
       <c r="B75" t="n">
-        <v>56692</v>
+        <v>56693</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9531,6 +9531,1127 @@
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128316450</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91984</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>654938</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6626130</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Carin von Köhler, Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128316251</v>
+      </c>
+      <c r="B77" t="n">
+        <v>90736</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>654871</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6626148</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Carin von Köhler, Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128316313</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91648</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>658</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>654919</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6626124</v>
+      </c>
+      <c r="S78" t="n">
+        <v>50</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Carin von Köhler, Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128316309</v>
+      </c>
+      <c r="B79" t="n">
+        <v>91352</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>654919</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6626124</v>
+      </c>
+      <c r="S79" t="n">
+        <v>50</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Carin von Köhler, Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128316342</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91806</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>654889</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6626152</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Carin von Köhler, Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128316297</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>654873</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6626177</v>
+      </c>
+      <c r="S81" t="n">
+        <v>50</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Carin von Köhler, Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128316139</v>
+      </c>
+      <c r="B82" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5733</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Såpfingersvamp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Ramaria lutea</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Vent.) Schild</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>654757</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6626122</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Carin von Köhler, Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128316547</v>
+      </c>
+      <c r="B83" t="n">
+        <v>92658</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>654875</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6626223</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Carin von Köhler, Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128316176</v>
+      </c>
+      <c r="B84" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>654790</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6626142</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Carin von Köhler, Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128316524</v>
+      </c>
+      <c r="B85" t="n">
+        <v>92670</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>654849</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6626229</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Carin von Köhler, Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128316236</v>
+      </c>
+      <c r="B86" t="n">
+        <v>85053</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>241</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Gransotdyna</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Camarops tubulina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>654874</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6626166</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Carin von Köhler, Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9536,7 +9536,7 @@
         <v>128316450</v>
       </c>
       <c r="B76" t="n">
-        <v>91984</v>
+        <v>91992</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>128316251</v>
       </c>
       <c r="B77" t="n">
-        <v>90736</v>
+        <v>90742</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>128316313</v>
       </c>
       <c r="B78" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>128316309</v>
       </c>
       <c r="B79" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>128316342</v>
       </c>
       <c r="B80" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>128316139</v>
       </c>
       <c r="B82" t="n">
-        <v>90878</v>
+        <v>90884</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>128316547</v>
       </c>
       <c r="B83" t="n">
-        <v>92658</v>
+        <v>92666</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>128316176</v>
       </c>
       <c r="B84" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10452,10 +10452,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128316524</v>
+        <v>128316236</v>
       </c>
       <c r="B85" t="n">
-        <v>92670</v>
+        <v>85056</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10463,21 +10463,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5449</v>
+        <v>241</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10490,10 +10490,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654849</v>
+        <v>654874</v>
       </c>
       <c r="R85" t="n">
-        <v>6626229</v>
+        <v>6626166</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10553,10 +10553,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128316236</v>
+        <v>128316524</v>
       </c>
       <c r="B86" t="n">
-        <v>85053</v>
+        <v>92678</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10564,21 +10564,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>241</v>
+        <v>5449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10591,10 +10591,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654874</v>
+        <v>654849</v>
       </c>
       <c r="R86" t="n">
-        <v>6626166</v>
+        <v>6626229</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9536,7 +9536,7 @@
         <v>128316450</v>
       </c>
       <c r="B76" t="n">
-        <v>91992</v>
+        <v>92084</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>128316251</v>
       </c>
       <c r="B77" t="n">
-        <v>90742</v>
+        <v>90834</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>128316313</v>
       </c>
       <c r="B78" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>128316309</v>
       </c>
       <c r="B79" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>128316342</v>
       </c>
       <c r="B80" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>128316139</v>
       </c>
       <c r="B82" t="n">
-        <v>90884</v>
+        <v>90976</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>128316547</v>
       </c>
       <c r="B83" t="n">
-        <v>92666</v>
+        <v>92758</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>128316176</v>
       </c>
       <c r="B84" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>128316236</v>
       </c>
       <c r="B85" t="n">
-        <v>85056</v>
+        <v>85142</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>128316524</v>
       </c>
       <c r="B86" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -10344,7 +10344,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Marie Kvarnström, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -10344,7 +10344,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marie Kvarnström, Carin von Köhler</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9536,7 +9536,7 @@
         <v>128316450</v>
       </c>
       <c r="B76" t="n">
-        <v>92084</v>
+        <v>92096</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>128316251</v>
       </c>
       <c r="B77" t="n">
-        <v>90834</v>
+        <v>90846</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9735,10 +9735,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128316313</v>
+        <v>128316309</v>
       </c>
       <c r="B78" t="n">
-        <v>91748</v>
+        <v>91464</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9746,21 +9746,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128316309</v>
+        <v>128316313</v>
       </c>
       <c r="B79" t="n">
-        <v>91452</v>
+        <v>91760</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9847,21 +9847,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9940,7 +9940,7 @@
         <v>128316342</v>
       </c>
       <c r="B80" t="n">
-        <v>91906</v>
+        <v>91918</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>128316139</v>
       </c>
       <c r="B82" t="n">
-        <v>90976</v>
+        <v>90988</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>128316547</v>
       </c>
       <c r="B83" t="n">
-        <v>92758</v>
+        <v>92770</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>128316176</v>
       </c>
       <c r="B84" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10452,10 +10452,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128316236</v>
+        <v>128316524</v>
       </c>
       <c r="B85" t="n">
-        <v>85142</v>
+        <v>92782</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10463,21 +10463,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>241</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10490,10 +10490,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654874</v>
+        <v>654849</v>
       </c>
       <c r="R85" t="n">
-        <v>6626166</v>
+        <v>6626229</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10553,10 +10553,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128316524</v>
+        <v>128316236</v>
       </c>
       <c r="B86" t="n">
-        <v>92770</v>
+        <v>85151</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10564,21 +10564,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>241</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10591,10 +10591,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654849</v>
+        <v>654874</v>
       </c>
       <c r="R86" t="n">
-        <v>6626229</v>
+        <v>6626166</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -10452,10 +10452,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128316524</v>
+        <v>128316236</v>
       </c>
       <c r="B85" t="n">
-        <v>92782</v>
+        <v>85151</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10463,21 +10463,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5449</v>
+        <v>241</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10490,10 +10490,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654849</v>
+        <v>654874</v>
       </c>
       <c r="R85" t="n">
-        <v>6626229</v>
+        <v>6626166</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10553,10 +10553,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128316236</v>
+        <v>128316524</v>
       </c>
       <c r="B86" t="n">
-        <v>85151</v>
+        <v>92782</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10564,21 +10564,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>241</v>
+        <v>5449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10591,10 +10591,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654874</v>
+        <v>654849</v>
       </c>
       <c r="R86" t="n">
-        <v>6626166</v>
+        <v>6626229</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9536,7 +9536,7 @@
         <v>128316450</v>
       </c>
       <c r="B76" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>128316251</v>
       </c>
       <c r="B77" t="n">
-        <v>90846</v>
+        <v>90848</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9735,10 +9735,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128316309</v>
+        <v>128316313</v>
       </c>
       <c r="B78" t="n">
-        <v>91464</v>
+        <v>91762</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9746,21 +9746,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128316313</v>
+        <v>128316309</v>
       </c>
       <c r="B79" t="n">
-        <v>91760</v>
+        <v>91466</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9847,21 +9847,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9940,7 +9940,7 @@
         <v>128316342</v>
       </c>
       <c r="B80" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>128316139</v>
       </c>
       <c r="B82" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>128316547</v>
       </c>
       <c r="B83" t="n">
-        <v>92770</v>
+        <v>92772</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Marie Kvarnström, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10354,7 +10354,7 @@
         <v>128316176</v>
       </c>
       <c r="B84" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>128316236</v>
       </c>
       <c r="B85" t="n">
-        <v>85151</v>
+        <v>85153</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>128316524</v>
       </c>
       <c r="B86" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9735,10 +9735,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128316313</v>
+        <v>128316309</v>
       </c>
       <c r="B78" t="n">
-        <v>91762</v>
+        <v>91466</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9746,21 +9746,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128316309</v>
+        <v>128316313</v>
       </c>
       <c r="B79" t="n">
-        <v>91466</v>
+        <v>91762</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9847,21 +9847,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marie Kvarnström, Carin von Köhler</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9735,10 +9735,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128316309</v>
+        <v>128316313</v>
       </c>
       <c r="B78" t="n">
-        <v>91466</v>
+        <v>91762</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9746,21 +9746,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128316313</v>
+        <v>128316309</v>
       </c>
       <c r="B79" t="n">
-        <v>91762</v>
+        <v>91466</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9847,21 +9847,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9536,7 +9536,7 @@
         <v>128316450</v>
       </c>
       <c r="B76" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>128316251</v>
       </c>
       <c r="B77" t="n">
-        <v>90848</v>
+        <v>90849</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9735,10 +9735,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128316313</v>
+        <v>128316309</v>
       </c>
       <c r="B78" t="n">
-        <v>91762</v>
+        <v>91467</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9746,21 +9746,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128316309</v>
+        <v>128316313</v>
       </c>
       <c r="B79" t="n">
-        <v>91466</v>
+        <v>91763</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9847,21 +9847,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9940,7 +9940,7 @@
         <v>128316342</v>
       </c>
       <c r="B80" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>128316139</v>
       </c>
       <c r="B82" t="n">
-        <v>90990</v>
+        <v>90991</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>128316547</v>
       </c>
       <c r="B83" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>128316176</v>
       </c>
       <c r="B84" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10452,10 +10452,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128316236</v>
+        <v>128316524</v>
       </c>
       <c r="B85" t="n">
-        <v>85153</v>
+        <v>92785</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10463,21 +10463,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>241</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10490,10 +10490,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654874</v>
+        <v>654849</v>
       </c>
       <c r="R85" t="n">
-        <v>6626166</v>
+        <v>6626229</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10553,10 +10553,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128316524</v>
+        <v>128316236</v>
       </c>
       <c r="B86" t="n">
-        <v>92784</v>
+        <v>85153</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10564,21 +10564,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>241</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10591,10 +10591,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654849</v>
+        <v>654874</v>
       </c>
       <c r="R86" t="n">
-        <v>6626229</v>
+        <v>6626166</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9536,7 +9536,7 @@
         <v>128316450</v>
       </c>
       <c r="B76" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>128316251</v>
       </c>
       <c r="B77" t="n">
-        <v>90849</v>
+        <v>90876</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>128316309</v>
       </c>
       <c r="B78" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>128316313</v>
       </c>
       <c r="B79" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>128316342</v>
       </c>
       <c r="B80" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>128316139</v>
       </c>
       <c r="B82" t="n">
-        <v>90991</v>
+        <v>91018</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>128316547</v>
       </c>
       <c r="B83" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>128316176</v>
       </c>
       <c r="B84" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>128316524</v>
       </c>
       <c r="B85" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Marie Kvarnström, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10556,7 +10556,7 @@
         <v>128316236</v>
       </c>
       <c r="B86" t="n">
-        <v>85153</v>
+        <v>85180</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9728,17 +9728,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Marie Kvarnström, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128316309</v>
+        <v>128316313</v>
       </c>
       <c r="B78" t="n">
-        <v>91494</v>
+        <v>91790</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9746,21 +9746,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9829,17 +9829,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Marie Kvarnström, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128316313</v>
+        <v>128316309</v>
       </c>
       <c r="B79" t="n">
-        <v>91790</v>
+        <v>91494</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9847,21 +9847,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Marie Kvarnström, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Marie Kvarnström, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Marie Kvarnström, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10452,10 +10452,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128316524</v>
+        <v>128316236</v>
       </c>
       <c r="B85" t="n">
-        <v>92812</v>
+        <v>85180</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10463,21 +10463,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5449</v>
+        <v>241</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10490,10 +10490,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654849</v>
+        <v>654874</v>
       </c>
       <c r="R85" t="n">
-        <v>6626229</v>
+        <v>6626166</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10553,10 +10553,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128316236</v>
+        <v>128316524</v>
       </c>
       <c r="B86" t="n">
-        <v>85180</v>
+        <v>92812</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10564,21 +10564,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>241</v>
+        <v>5449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10591,10 +10591,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654874</v>
+        <v>654849</v>
       </c>
       <c r="R86" t="n">
-        <v>6626166</v>
+        <v>6626229</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9536,7 +9536,7 @@
         <v>128316450</v>
       </c>
       <c r="B76" t="n">
-        <v>92126</v>
+        <v>92136</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>128316251</v>
       </c>
       <c r="B77" t="n">
-        <v>90876</v>
+        <v>90886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marie Kvarnström, Carin von Köhler</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9738,7 +9738,7 @@
         <v>128316313</v>
       </c>
       <c r="B78" t="n">
-        <v>91790</v>
+        <v>91800</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marie Kvarnström, Carin von Köhler</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9839,7 +9839,7 @@
         <v>128316309</v>
       </c>
       <c r="B79" t="n">
-        <v>91494</v>
+        <v>91504</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marie Kvarnström, Carin von Köhler</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9940,7 +9940,7 @@
         <v>128316342</v>
       </c>
       <c r="B80" t="n">
-        <v>91948</v>
+        <v>91958</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Kvarnström, Carin von Köhler</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marie Kvarnström, Carin von Köhler</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10152,7 +10152,7 @@
         <v>128316139</v>
       </c>
       <c r="B82" t="n">
-        <v>91018</v>
+        <v>91028</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>128316547</v>
       </c>
       <c r="B83" t="n">
-        <v>92800</v>
+        <v>92810</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>128316176</v>
       </c>
       <c r="B84" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>128316236</v>
       </c>
       <c r="B85" t="n">
-        <v>85180</v>
+        <v>85184</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marie Kvarnström, Carin von Köhler</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10556,7 +10556,7 @@
         <v>128316524</v>
       </c>
       <c r="B86" t="n">
-        <v>92812</v>
+        <v>92823</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10566,21 +10566,12 @@
       <c r="E86" t="n">
         <v>5449</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -10452,10 +10452,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128316236</v>
+        <v>128316524</v>
       </c>
       <c r="B85" t="n">
-        <v>85184</v>
+        <v>92823</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10463,23 +10463,14 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>241</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Gransotdyna</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -10490,10 +10481,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654874</v>
+        <v>654849</v>
       </c>
       <c r="R85" t="n">
-        <v>6626166</v>
+        <v>6626229</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10553,10 +10544,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128316524</v>
+        <v>128316236</v>
       </c>
       <c r="B86" t="n">
-        <v>92823</v>
+        <v>85184</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10564,14 +10555,23 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>241</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Gransotdyna</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Camarops tubulina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -10582,10 +10582,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654849</v>
+        <v>654874</v>
       </c>
       <c r="R86" t="n">
-        <v>6626229</v>
+        <v>6626166</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9735,10 +9735,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128316313</v>
+        <v>128316309</v>
       </c>
       <c r="B78" t="n">
-        <v>91800</v>
+        <v>91504</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9746,21 +9746,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128316309</v>
+        <v>128316313</v>
       </c>
       <c r="B79" t="n">
-        <v>91504</v>
+        <v>91800</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9847,21 +9847,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10452,10 +10452,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128316524</v>
+        <v>128316236</v>
       </c>
       <c r="B85" t="n">
-        <v>92823</v>
+        <v>85184</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10463,14 +10463,23 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5449</v>
+        <v>241</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Gransotdyna</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Camarops tubulina</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -10481,10 +10490,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654849</v>
+        <v>654874</v>
       </c>
       <c r="R85" t="n">
-        <v>6626229</v>
+        <v>6626166</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10544,10 +10553,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128316236</v>
+        <v>128316524</v>
       </c>
       <c r="B86" t="n">
-        <v>85184</v>
+        <v>92823</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10555,23 +10564,14 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>241</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Gransotdyna</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -10582,10 +10582,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654874</v>
+        <v>654849</v>
       </c>
       <c r="R86" t="n">
-        <v>6626166</v>
+        <v>6626229</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10643,6 +10643,147 @@
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>132016415</v>
+      </c>
+      <c r="B87" t="n">
+        <v>92300</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>654885</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6626320</v>
+      </c>
+      <c r="S87" t="n">
+        <v>25</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -10648,7 +10648,7 @@
         <v>132016415</v>
       </c>
       <c r="B87" t="n">
-        <v>92300</v>
+        <v>92301</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY87"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10648,7 +10648,7 @@
         <v>132016415</v>
       </c>
       <c r="B87" t="n">
-        <v>92301</v>
+        <v>92306</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10783,6 +10783,275 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>132131462</v>
+      </c>
+      <c r="B88" t="n">
+        <v>91866</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>654853</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6626349</v>
+      </c>
+      <c r="S88" t="n">
+        <v>25</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>132131402</v>
+      </c>
+      <c r="B89" t="n">
+        <v>92501</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>654853</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6626349</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -10648,7 +10648,7 @@
         <v>132016415</v>
       </c>
       <c r="B87" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>132131462</v>
       </c>
       <c r="B88" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>132131402</v>
       </c>
       <c r="B89" t="n">
-        <v>92544</v>
+        <v>92547</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11053,6 +11053,132 @@
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>132632842</v>
+      </c>
+      <c r="B90" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>654863</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6626472</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -10648,7 +10648,7 @@
         <v>132016415</v>
       </c>
       <c r="B87" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>132131462</v>
       </c>
       <c r="B88" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>132131402</v>
       </c>
       <c r="B89" t="n">
-        <v>92547</v>
+        <v>92553</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>132632842</v>
       </c>
       <c r="B90" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -10648,7 +10648,7 @@
         <v>132016415</v>
       </c>
       <c r="B87" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>132131462</v>
       </c>
       <c r="B88" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>132131402</v>
       </c>
       <c r="B89" t="n">
-        <v>92553</v>
+        <v>92563</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>132632842</v>
       </c>
       <c r="B90" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -11058,7 +11058,7 @@
         <v>132632842</v>
       </c>
       <c r="B90" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY105"/>
+  <dimension ref="A1:AZ105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128316236</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98609077</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128316313</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132768310</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639049</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639050</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639051</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639052</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639053</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639054</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98803055</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1936,6 +1996,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98803341</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2044,6 +2109,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98898037</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2152,6 +2222,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98899198</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2260,6 +2335,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98936072</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98940194</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2476,6 +2561,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99297659</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2597,6 +2687,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100500990</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2713,6 +2808,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100501366</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2834,6 +2934,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100501574</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2942,6 +3047,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112249602</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3043,6 +3153,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128316309</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3141,6 +3256,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639082</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3252,6 +3372,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96087730</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3360,6 +3485,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98606593</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3457,6 +3587,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639063</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3554,6 +3689,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639064</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3651,6 +3791,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639065</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3759,6 +3904,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98642394</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3876,6 +4026,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98803089</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3984,6 +4139,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98827190</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4092,6 +4252,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98899194</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4204,6 +4369,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98936059</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4321,6 +4491,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99297650</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4442,6 +4617,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100500931</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4563,6 +4743,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100501393</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4672,6 +4857,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128316342</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4813,6 +5003,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132016415</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4954,6 +5149,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132131402</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5085,6 +5285,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112088991</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5207,6 +5412,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96054661</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5319,6 +5529,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98607686</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5420,6 +5635,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128316547</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5538,6 +5758,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98632087</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5651,6 +5876,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98632168</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5768,6 +5998,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104436773</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5876,6 +6111,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112090588</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5993,6 +6233,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112249659</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6101,6 +6346,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96053551</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6198,6 +6448,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639056</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6317,6 +6572,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96052852</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6438,6 +6698,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100501545</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6539,6 +6804,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128316176</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6656,6 +6926,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98607723</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6763,6 +7038,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98608355</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6871,6 +7151,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98606528</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6988,6 +7273,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98608061</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7102,6 +7392,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98638479</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7216,6 +7511,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98638538</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7328,6 +7628,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98899305</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7429,6 +7734,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128316251</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7530,6 +7840,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128316139</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7638,6 +7953,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96053454</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7750,6 +8070,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98632141</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7851,6 +8176,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128316450</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7975,6 +8305,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100400258</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8101,6 +8436,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109511138</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8227,6 +8567,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109843058</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8324,6 +8669,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639070</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8446,6 +8796,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98677381</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8564,6 +8919,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99297808</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8690,6 +9050,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100388318</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8808,6 +9173,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98804218</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8930,6 +9300,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98765518</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9052,6 +9427,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98677366</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9155,6 +9535,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128316297</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9273,6 +9658,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96053393</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9391,6 +9781,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98607855</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9500,6 +9895,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98608115</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9618,6 +10018,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98608409</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9736,6 +10141,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98608502</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9858,6 +10268,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99035628</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9976,6 +10391,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99250188</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10094,6 +10514,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99298343</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10203,6 +10628,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100191450</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10312,6 +10742,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100384691</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10429,6 +10864,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104297499</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10541,6 +10981,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106211456</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10662,6 +11107,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108944701</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10788,6 +11238,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112249551</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10905,6 +11360,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112251982</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11014,6 +11474,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98609287</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11132,6 +11597,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98642582</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11258,6 +11728,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132632842</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11370,6 +11845,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104297588</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11491,6 +11971,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112090750</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11599,6 +12084,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98609195</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11707,6 +12197,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96054296</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11826,6 +12321,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100501116</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11948,6 +12448,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112265989</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12065,6 +12570,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112266023</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12173,6 +12683,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112267670</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12285,6 +12800,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98936021</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12393,8 +12913,119 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104259921</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ105"/>
+  <dimension ref="A1:AZ106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9181,10 +9181,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>98765518</v>
+        <v>135987246</v>
       </c>
       <c r="B75" t="n">
-        <v>58327</v>
+        <v>57977</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9192,16 +9192,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9214,15 +9214,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9231,10 +9225,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>654794</v>
+        <v>654915</v>
       </c>
       <c r="R75" t="n">
-        <v>6626077</v>
+        <v>6626038</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9261,22 +9255,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9302,33 +9296,33 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98765518</t>
+          <t>https://artportalen.se/Sighting/135987246</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>98677366</v>
+        <v>98765518</v>
       </c>
       <c r="B76" t="n">
-        <v>58112</v>
+        <v>58327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9338,7 +9332,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -9349,7 +9343,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9358,10 +9352,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>655016</v>
+        <v>654794</v>
       </c>
       <c r="R76" t="n">
-        <v>6626045</v>
+        <v>6626077</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9388,22 +9382,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9429,59 +9423,69 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98677366</t>
+          <t>https://artportalen.se/Sighting/98765518</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128316297</v>
+        <v>98677366</v>
       </c>
       <c r="B77" t="n">
-        <v>8455</v>
+        <v>58112</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>103020</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tagstaskogen, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>654873</v>
+        <v>655016</v>
       </c>
       <c r="R77" t="n">
-        <v>6626177</v>
+        <v>6626045</v>
       </c>
       <c r="S77" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9505,12 +9509,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2022-02-19</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2022-02-19</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9519,83 +9533,76 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128316297</t>
+          <t>https://artportalen.se/Sighting/98677366</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>96053393</v>
+        <v>128316297</v>
       </c>
       <c r="B78" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>654985</v>
+        <v>654873</v>
       </c>
       <c r="R78" t="n">
-        <v>6626101</v>
+        <v>6626177</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9619,22 +9626,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:31</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:31</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9643,30 +9640,31 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96053393</t>
+          <t>https://artportalen.se/Sighting/128316297</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>98607855</v>
+        <v>96053393</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -9696,7 +9694,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9708,14 +9706,14 @@
       <c r="L79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>654901</v>
+        <v>654985</v>
       </c>
       <c r="R79" t="n">
-        <v>6626274</v>
+        <v>6626101</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9742,22 +9740,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9772,24 +9770,24 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98607855</t>
+          <t>https://artportalen.se/Sighting/96053393</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>98608115</v>
+        <v>98607855</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9817,7 +9815,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -9826,10 +9833,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>654843</v>
+        <v>654901</v>
       </c>
       <c r="R80" t="n">
-        <v>6626288</v>
+        <v>6626274</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9861,7 +9868,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9871,7 +9878,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9897,13 +9904,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98608115</t>
+          <t>https://artportalen.se/Sighting/98607855</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>98608409</v>
+        <v>98608115</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9931,16 +9938,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -9949,10 +9947,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>654854</v>
+        <v>654843</v>
       </c>
       <c r="R81" t="n">
-        <v>6626301</v>
+        <v>6626288</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9984,7 +9982,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9994,7 +9992,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10020,13 +10018,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98608409</t>
+          <t>https://artportalen.se/Sighting/98608115</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>98608502</v>
+        <v>98608409</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -10056,7 +10054,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10072,10 +10070,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>654919</v>
+        <v>654854</v>
       </c>
       <c r="R82" t="n">
-        <v>6626271</v>
+        <v>6626301</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10107,7 +10105,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10117,7 +10115,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10143,13 +10141,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98608502</t>
+          <t>https://artportalen.se/Sighting/98608409</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>99035628</v>
+        <v>98608502</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -10184,14 +10182,10 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10202,7 +10196,7 @@
         <v>654919</v>
       </c>
       <c r="R83" t="n">
-        <v>6626274</v>
+        <v>6626271</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10229,22 +10223,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10270,13 +10264,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99035628</t>
+          <t>https://artportalen.se/Sighting/98608502</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>99250188</v>
+        <v>99035628</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -10306,7 +10300,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10314,7 +10308,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10322,13 +10320,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>654914</v>
+        <v>654919</v>
       </c>
       <c r="R84" t="n">
-        <v>6626178</v>
+        <v>6626274</v>
       </c>
       <c r="S84" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10352,22 +10350,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2022-03-19</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2022-03-19</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10393,13 +10391,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99250188</t>
+          <t>https://artportalen.se/Sighting/99035628</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>99298343</v>
+        <v>99250188</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -10445,13 +10443,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654976</v>
+        <v>654914</v>
       </c>
       <c r="R85" t="n">
-        <v>6626119</v>
+        <v>6626178</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10475,22 +10473,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2022-03-19</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2022-03-19</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10516,13 +10514,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99298343</t>
+          <t>https://artportalen.se/Sighting/99250188</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>100191450</v>
+        <v>99298343</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -10550,7 +10548,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
@@ -10559,10 +10566,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654885</v>
+        <v>654976</v>
       </c>
       <c r="R86" t="n">
-        <v>6626320</v>
+        <v>6626119</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10589,22 +10596,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10630,13 +10637,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100191450</t>
+          <t>https://artportalen.se/Sighting/99298343</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>100384691</v>
+        <v>100191450</v>
       </c>
       <c r="B87" t="n">
         <v>99118</v>
@@ -10673,10 +10680,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>654875</v>
+        <v>654885</v>
       </c>
       <c r="R87" t="n">
-        <v>6626261</v>
+        <v>6626320</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10703,22 +10710,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10744,13 +10751,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100384691</t>
+          <t>https://artportalen.se/Sighting/100191450</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>104297499</v>
+        <v>100384691</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -10778,27 +10785,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>654801</v>
+        <v>654875</v>
       </c>
       <c r="R88" t="n">
-        <v>6626326</v>
+        <v>6626261</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10825,22 +10824,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10866,13 +10865,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104297499</t>
+          <t>https://artportalen.se/Sighting/100384691</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>106211456</v>
+        <v>104297499</v>
       </c>
       <c r="B89" t="n">
         <v>99118</v>
@@ -10902,20 +10901,25 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Tagstahammaren, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>654947</v>
+        <v>654801</v>
       </c>
       <c r="R89" t="n">
-        <v>6626192</v>
+        <v>6626326</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10942,22 +10946,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10983,13 +10987,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106211456</t>
+          <t>https://artportalen.se/Sighting/104297499</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>108944701</v>
+        <v>106211456</v>
       </c>
       <c r="B90" t="n">
         <v>99118</v>
@@ -11019,29 +11023,20 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Tagstahammaren, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>654877</v>
+        <v>654947</v>
       </c>
       <c r="R90" t="n">
-        <v>6626241</v>
+        <v>6626192</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -11068,22 +11063,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11109,13 +11104,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108944701</t>
+          <t>https://artportalen.se/Sighting/106211456</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112249551</v>
+        <v>108944701</v>
       </c>
       <c r="B91" t="n">
         <v>99118</v>
@@ -11145,7 +11140,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11160,17 +11155,17 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Knivsta, Knivsta, Upl</t>
+          <t>Tagstahammaren, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>654785</v>
+        <v>654877</v>
       </c>
       <c r="R91" t="n">
-        <v>6626333</v>
+        <v>6626241</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11194,22 +11189,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11220,11 +11215,6 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -11240,13 +11230,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112249551</t>
+          <t>https://artportalen.se/Sighting/108944701</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112251982</v>
+        <v>112249551</v>
       </c>
       <c r="B92" t="n">
         <v>99118</v>
@@ -11276,25 +11266,29 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Tagstahammaren, nära kärret, Tagstahammaren, nära kärret, Upl</t>
+          <t>Knivsta, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>654747</v>
+        <v>654785</v>
       </c>
       <c r="R92" t="n">
-        <v>6626129</v>
+        <v>6626333</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11326,7 +11320,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11336,7 +11330,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11347,6 +11341,11 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11362,56 +11361,64 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112251982</t>
+          <t>https://artportalen.se/Sighting/112249551</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>98609287</v>
+        <v>112251982</v>
       </c>
       <c r="B93" t="n">
-        <v>101326</v>
+        <v>99118</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstahammaren, nära kärret, Tagstahammaren, nära kärret, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>654998</v>
+        <v>654747</v>
       </c>
       <c r="R93" t="n">
-        <v>6626133</v>
+        <v>6626129</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11435,22 +11442,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11476,13 +11483,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98609287</t>
+          <t>https://artportalen.se/Sighting/112251982</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>98642582</v>
+        <v>98609287</v>
       </c>
       <c r="B94" t="n">
         <v>101326</v>
@@ -11510,16 +11517,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -11528,10 +11526,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>654896</v>
+        <v>654998</v>
       </c>
       <c r="R94" t="n">
-        <v>6626428</v>
+        <v>6626133</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11558,22 +11556,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11599,16 +11597,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98642582</t>
+          <t>https://artportalen.se/Sighting/98609287</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132632842</v>
+        <v>98642582</v>
       </c>
       <c r="B95" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11635,7 +11633,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11643,21 +11641,18 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>654863</v>
+        <v>654896</v>
       </c>
       <c r="R95" t="n">
-        <v>6626472</v>
+        <v>6626428</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11684,22 +11679,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11710,11 +11705,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11730,16 +11720,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132632842</t>
+          <t>https://artportalen.se/Sighting/98642582</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>104297588</v>
+        <v>132632842</v>
       </c>
       <c r="B96" t="n">
-        <v>101228</v>
+        <v>101403</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11747,39 +11737,48 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>654786</v>
+        <v>654863</v>
       </c>
       <c r="R96" t="n">
-        <v>6626345</v>
+        <v>6626472</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11806,22 +11805,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11832,6 +11831,11 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11847,13 +11851,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104297588</t>
+          <t>https://artportalen.se/Sighting/132632842</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112090750</v>
+        <v>104297588</v>
       </c>
       <c r="B97" t="n">
         <v>101228</v>
@@ -11886,29 +11890,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Knivsta, Knivsta, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>654798</v>
+        <v>654786</v>
       </c>
       <c r="R97" t="n">
-        <v>6626355</v>
+        <v>6626345</v>
       </c>
       <c r="S97" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11932,22 +11927,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11973,16 +11968,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112090750</t>
+          <t>https://artportalen.se/Sighting/104297588</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>98609195</v>
+        <v>112090750</v>
       </c>
       <c r="B98" t="n">
-        <v>99038</v>
+        <v>101228</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11990,22 +11985,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>223597</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12015,23 +12014,22 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Knivsta, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>654998</v>
+        <v>654798</v>
       </c>
       <c r="R98" t="n">
-        <v>6626133</v>
+        <v>6626355</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12055,12 +12053,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12086,52 +12094,62 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98609195</t>
+          <t>https://artportalen.se/Sighting/112090750</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>96054296</v>
+        <v>98609195</v>
       </c>
       <c r="B99" t="n">
-        <v>93194</v>
+        <v>99038</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>239737</v>
+        <v>223597</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knölig taggsvamp</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum cumulatum</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>K.A.Harrison</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Tagstaskogen, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>654742</v>
+        <v>654998</v>
       </c>
       <c r="R99" t="n">
-        <v>6626141</v>
+        <v>6626133</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -12158,22 +12176,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12188,24 +12196,24 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96054296</t>
+          <t>https://artportalen.se/Sighting/98609195</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>100501116</v>
+        <v>96054296</v>
       </c>
       <c r="B100" t="n">
         <v>93194</v>
@@ -12233,31 +12241,21 @@
           <t>K.A.Harrison</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Tagsta, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>654735</v>
+        <v>654742</v>
       </c>
       <c r="R100" t="n">
-        <v>6626144</v>
+        <v>6626141</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12281,17 +12279,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2021-09-12</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Fjolårsexemplar</t>
+          <t>2021-09-12</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12300,36 +12303,30 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>Intill sten på stig</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Patrick Fritzson</t>
+          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100501116</t>
+          <t>https://artportalen.se/Sighting/96054296</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>112265989</v>
+        <v>100501116</v>
       </c>
       <c r="B101" t="n">
         <v>93194</v>
@@ -12359,7 +12356,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12368,16 +12365,17 @@
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Tagstahammaren, nära kärret, Tagstahammaren, nära kärret, Upl</t>
+          <t>Tagsta, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>654747</v>
+        <v>654735</v>
       </c>
       <c r="R101" t="n">
-        <v>6626129</v>
+        <v>6626144</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12404,22 +12402,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>15:12</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>15:12</t>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Fjolårsexemplar</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12428,35 +12421,36 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>Intill sten på stig</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Björn Bråvander, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112265989</t>
+          <t>https://artportalen.se/Sighting/100501116</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>112266023</v>
+        <v>112265989</v>
       </c>
       <c r="B102" t="n">
         <v>93194</v>
@@ -12497,14 +12491,14 @@
       <c r="K102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Knivsta, Knivsta, Upl</t>
+          <t>Tagstahammaren, nära kärret, Tagstahammaren, nära kärret, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>654744</v>
+        <v>654747</v>
       </c>
       <c r="R102" t="n">
-        <v>6626117</v>
+        <v>6626129</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12536,7 +12530,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12546,7 +12540,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12557,6 +12551,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12572,13 +12571,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112266023</t>
+          <t>https://artportalen.se/Sighting/112265989</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>112267670</v>
+        <v>112266023</v>
       </c>
       <c r="B103" t="n">
         <v>93194</v>
@@ -12606,7 +12605,16 @@
           <t>K.A.Harrison</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12614,10 +12622,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>654750</v>
+        <v>654744</v>
       </c>
       <c r="R103" t="n">
-        <v>6626105</v>
+        <v>6626117</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12649,7 +12657,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12659,7 +12667,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12685,59 +12693,55 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112267670</t>
+          <t>https://artportalen.se/Sighting/112266023</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>98936021</v>
+        <v>112267670</v>
       </c>
       <c r="B104" t="n">
-        <v>92329</v>
+        <v>93194</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6040186</v>
+        <v>239737</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knölig taggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hydnellum cumulatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>K.A.Harrison</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Knivsta, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>654936</v>
+        <v>654750</v>
       </c>
       <c r="R104" t="n">
-        <v>6626103</v>
+        <v>6626105</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12761,22 +12765,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2022-03-06</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2022-03-06</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12791,24 +12795,24 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98936021</t>
+          <t>https://artportalen.se/Sighting/112267670</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>104259921</v>
+        <v>98936021</v>
       </c>
       <c r="B105" t="n">
         <v>92329</v>
@@ -12836,7 +12840,11 @@
           <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -12844,10 +12852,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>654969</v>
+        <v>654936</v>
       </c>
       <c r="R105" t="n">
-        <v>6626078</v>
+        <v>6626103</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12874,22 +12882,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
+          <t>2022-03-06</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
+          <t>2022-03-06</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12904,16 +12912,129 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Elisabet Ottosson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Elisabet Ottosson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98936021</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104259921</v>
+      </c>
+      <c r="B106" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>654969</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6626078</v>
+      </c>
+      <c r="S106" t="n">
+        <v>25</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104259921</t>
         </is>
@@ -13025,6 +13146,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9184,7 +9184,7 @@
         <v>135987246</v>
       </c>
       <c r="B75" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9184,7 +9184,7 @@
         <v>135987246</v>
       </c>
       <c r="B75" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9184,7 +9184,7 @@
         <v>135987246</v>
       </c>
       <c r="B75" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9184,7 +9184,7 @@
         <v>135987246</v>
       </c>
       <c r="B75" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9184,7 +9184,7 @@
         <v>135987246</v>
       </c>
       <c r="B75" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -9184,7 +9184,7 @@
         <v>135987246</v>
       </c>
       <c r="B75" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
